--- a/artfynd/A 44500-2019 artfynd.xlsx
+++ b/artfynd/A 44500-2019 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 44500-2019 artfynd.xlsx
+++ b/artfynd/A 44500-2019 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1923,6 +1923,240 @@
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>125572746</v>
+      </c>
+      <c r="B12" t="n">
+        <v>97147</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Dalen, Dalen, Vg</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>476163</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6504618</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Karlsborg</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Undenäs</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>16:49</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>16:49</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Boel Nilsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Boel Nilsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>125571740</v>
+      </c>
+      <c r="B13" t="n">
+        <v>78947</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Stenkällegården, Stenkällegården, Vg</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>476166</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6504545</v>
+      </c>
+      <c r="S13" t="n">
+        <v>30</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Karlsborg</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Undenäs</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>16:26</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>16:26</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Välutbredd på de gamla granarna ovanför branten.</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Boel Nilsson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Boel Nilsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 44500-2019 artfynd.xlsx
+++ b/artfynd/A 44500-2019 artfynd.xlsx
@@ -1925,10 +1925,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125572746</v>
+        <v>125571740</v>
       </c>
       <c r="B12" t="n">
-        <v>97147</v>
+        <v>78947</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1937,46 +1937,41 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Dalen, Dalen, Vg</t>
+          <t>Stenkällegården, Stenkällegården, Vg</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>476163</v>
+        <v>476166</v>
       </c>
       <c r="R12" t="n">
-        <v>6504618</v>
+        <v>6504545</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2005,7 +2000,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2015,7 +2010,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>16:26</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Välutbredd på de gamla granarna ovanför branten.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2042,10 +2042,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125571740</v>
+        <v>125572746</v>
       </c>
       <c r="B13" t="n">
-        <v>78947</v>
+        <v>97147</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2054,41 +2054,46 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Stenkällegården, Stenkällegården, Vg</t>
+          <t>Dalen, Dalen, Vg</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>476166</v>
+        <v>476163</v>
       </c>
       <c r="R13" t="n">
-        <v>6504545</v>
+        <v>6504618</v>
       </c>
       <c r="S13" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2117,7 +2122,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2127,12 +2132,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:26</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Välutbredd på de gamla granarna ovanför branten.</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 44500-2019 artfynd.xlsx
+++ b/artfynd/A 44500-2019 artfynd.xlsx
@@ -1925,53 +1925,53 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125571740</v>
+        <v>125572746</v>
       </c>
       <c r="B12" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97202</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Stenkällegården, Stenkällegården, Vg</t>
+          <t>Dalen, Dalen, Vg</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>476166</v>
+        <v>476163</v>
       </c>
       <c r="R12" t="n">
-        <v>6504545</v>
+        <v>6504618</v>
       </c>
       <c r="S12" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2000,7 +2000,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2010,12 +2010,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:26</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Välutbredd på de gamla granarna ovanför branten.</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2042,58 +2037,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125572746</v>
+        <v>125571740</v>
       </c>
       <c r="B13" t="n">
-        <v>97147</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78967</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Dalen, Dalen, Vg</t>
+          <t>Stenkällegården, Stenkällegården, Vg</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>476163</v>
+        <v>476166</v>
       </c>
       <c r="R13" t="n">
-        <v>6504618</v>
+        <v>6504545</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2122,7 +2107,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2132,7 +2117,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>16:26</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Välutbredd på de gamla granarna ovanför branten.</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 44500-2019 artfynd.xlsx
+++ b/artfynd/A 44500-2019 artfynd.xlsx
@@ -1928,7 +1928,7 @@
         <v>125572746</v>
       </c>
       <c r="B12" t="n">
-        <v>97202</v>
+        <v>97209</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 44500-2019 artfynd.xlsx
+++ b/artfynd/A 44500-2019 artfynd.xlsx
@@ -1928,7 +1928,7 @@
         <v>125572746</v>
       </c>
       <c r="B12" t="n">
-        <v>97209</v>
+        <v>97212</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
         <v>125571740</v>
       </c>
       <c r="B13" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 44500-2019 artfynd.xlsx
+++ b/artfynd/A 44500-2019 artfynd.xlsx
@@ -1928,7 +1928,7 @@
         <v>125572746</v>
       </c>
       <c r="B12" t="n">
-        <v>97212</v>
+        <v>97216</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
         <v>125571740</v>
       </c>
       <c r="B13" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 44500-2019 artfynd.xlsx
+++ b/artfynd/A 44500-2019 artfynd.xlsx
@@ -1928,7 +1928,7 @@
         <v>125572746</v>
       </c>
       <c r="B12" t="n">
-        <v>97216</v>
+        <v>97217</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 44500-2019 artfynd.xlsx
+++ b/artfynd/A 44500-2019 artfynd.xlsx
@@ -1928,7 +1928,7 @@
         <v>125572746</v>
       </c>
       <c r="B12" t="n">
-        <v>97217</v>
+        <v>97219</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
         <v>125571740</v>
       </c>
       <c r="B13" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 44500-2019 artfynd.xlsx
+++ b/artfynd/A 44500-2019 artfynd.xlsx
@@ -1928,7 +1928,7 @@
         <v>125572746</v>
       </c>
       <c r="B12" t="n">
-        <v>97219</v>
+        <v>97221</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 44500-2019 artfynd.xlsx
+++ b/artfynd/A 44500-2019 artfynd.xlsx
@@ -1928,7 +1928,7 @@
         <v>125572746</v>
       </c>
       <c r="B12" t="n">
-        <v>97221</v>
+        <v>97223</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
